--- a/inputs/CEREBRO_Input_Nusinersen.xlsx
+++ b/inputs/CEREBRO_Input_Nusinersen.xlsx
@@ -787,14 +787,14 @@
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t>CEREBRO-X v22.1   ⟶   Drug Input  (Validation Set: 3 drug types)</t>
+          <t>CEREBRO-X v22.1   ⟶   Drug Input  (Nusinersen — antisense oligonucleotide, SMA)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3-drug validation: monoclonal antibody + small molecule + antisense oligonucleotide. Tests all FDA categories the pipeline must support.</t>
+          <t>Single-drug validation: 2'-MOE phosphorothioate ASO, FDA-approved standard of care.</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Drug 3  (Nusinersen — 2'-MOE phosphorothioate ASO, SMA)</t>
-        </is>
-      </c>
+      <c r="A5" s="5" t="n"/>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="8" t="n"/>
